--- a/VerveStacks_ETH_grids_kan10/vt_vervestacks_ETH_v1.xlsx
+++ b/VerveStacks_ETH_grids_kan10/vt_vervestacks_ETH_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ETH_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9642A767-98BC-4748-89D6-B0C7F835F8AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E740BD94-7132-4EB0-97E4-F2BEC5FD5672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0A679ACE-9468-43CE-847D-A2A9DEA0ADDC}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E621535F-C38E-4910-9A6E-CA20FDFB4DA3}"/>
   </bookViews>
   <sheets>
     <sheet name="additional_hydro_pot" sheetId="5" r:id="rId1"/>
@@ -1061,7 +1061,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D321900-FD36-488A-9D81-640118B3469E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F71A0D-191F-4640-AE98-BED88445B9E6}">
   <dimension ref="B9:O13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1243,7 +1243,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E031DCA1-41D1-4E4A-BDA4-FCD89ADB2D62}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B480020-C800-4451-B618-AC1BBC30354C}">
   <dimension ref="B9:V10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1323,7 +1323,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5297337C-2C61-49DA-8D84-5C3B4D4AA88C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78CFF9B0-4231-4372-AE0B-FE6D2B7309DE}">
   <dimension ref="B9:W44"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3439,7 +3439,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF3A4736-45C1-41B4-8687-9EEA943BE587}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BE11A1E-162F-4730-A181-A0A8321E8362}">
   <dimension ref="B9:W48"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5707,7 +5707,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9759E493-CB0C-4AFB-B078-3C2F5E0E151B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{776563AA-0387-440F-B205-AF694B987FE4}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
